--- a/manman-278/colors.xlsx
+++ b/manman-278/colors.xlsx
@@ -3002,12 +3002,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>原始查询名</t>
+          <t>系列短名</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>鷯担瞰漫家 / 漫漫家</t>
+          <t>漫漫家</t>
         </is>
       </c>
     </row>

--- a/manman-278/colors.xlsx
+++ b/manman-278/colors.xlsx
@@ -1,31 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="信息" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_A" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_B" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_C" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_D" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_DH" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_E" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_F" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_G" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_IC" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_N" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_Q" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_R" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_YX" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_Y" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_L" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_P" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_T" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_S" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="信息" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="01_A" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="02_B" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="03_C" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="04_D" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="05_DH" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="06_E" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="07_F" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="08_G" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="09_IC" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="10_N" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="11_Q" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="12_R" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="13_YX" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="14_Y" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="15_L" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="16_P" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="17_T" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="18_S" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/manman-278/colors.xlsx
+++ b/manman-278/colors.xlsx
@@ -1,31 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="信息" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="01_A" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="02_B" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="03_C" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="04_D" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="05_DH" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="06_E" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="07_F" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="08_G" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="09_IC" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="10_N" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="11_Q" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="12_R" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="13_YX" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="14_Y" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="15_L" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="16_P" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="17_T" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="18_S" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="信息" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_A" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_B" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_C" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_D" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_DH" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_E" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_F" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_G" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_IC" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_N" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_Q" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_R" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_YX" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_Y" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_L" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_P" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_T" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_S" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
